--- a/public/roster-template.xlsx
+++ b/public/roster-template.xlsx
@@ -12,6 +12,7 @@
   <cols>
     <col min="1" max="1" width="16"/>
     <col min="2" max="4" width="9"/>
+    <col min="5" max="5" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35,6 +36,11 @@
           <t xml:space="preserve">Qty</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Title</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -54,6 +60,11 @@
       </c>
       <c r="D2">
         <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAPTAIN</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -96,32 +107,46 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Notes:</t>
-        </is>
-      </c>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">One shirt per row — delete the examples and add your team.</t>
+          <t xml:space="preserve">Notes:</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Size must be one the product offers (e.g. S, M, L, XL).</t>
+          <t xml:space="preserve">One shirt per row — delete the examples and add your team.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">In the designer: Names &amp; Numbers -&gt; Paste a list -&gt; paste these rows.</t>
+          <t xml:space="preserve">Title is optional (e.g. CAPTAIN, COACH, EST. 2024). Leave the cell blank if unused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Keep this column order: Name, Number, Size, Qty, Title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Size must be one the product offers (e.g. S, M, L, XL).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In the designer: Names &amp; Numbers → Paste a list → paste these rows (header row included is fine).</t>
         </is>
       </c>
     </row>
